--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0138.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0138.xlsx
@@ -13444,7 +13444,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Ta biết ngươi sẽ không ngồi yên. Nếu ngươi quyết định đến, hãy theo tọa độ mà Shiratori của ta để lại.</t>
+          <t>Tao biết mày sẽ không ngồi yên. Nếu mày quyết định đến, hãy theo tọa độ mà Shiratori của tao để lại.</t>
         </is>
       </c>
     </row>
@@ -27554,7 +27554,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Nếu tình cờ gặp bất kỳ Soliskin nào lạc đường, bảo chúng đến tìm ta ở đây được không?</t>
+          <t>Nếu tình cờ gặp bất kỳ Soliskin nào lạc đường, bảo chúng đến tìm tao ở đây được không?</t>
         </is>
       </c>
     </row>
